--- a/data/trans_dic/IP15-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,17; 30,06</t>
+          <t>18,47; 29,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,14; 28,84</t>
+          <t>17,06; 29,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,42; 24,94</t>
+          <t>13,03; 24,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,41; 28,34</t>
+          <t>16,3; 29,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,05; 24,29</t>
+          <t>14,0; 24,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,51; 27,86</t>
+          <t>17,13; 28,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,61; 22,35</t>
+          <t>11,45; 21,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,96; 26,92</t>
+          <t>13,59; 27,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 25,54</t>
+          <t>17,57; 25,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,64; 27,0</t>
+          <t>18,67; 26,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,42; 21,19</t>
+          <t>13,4; 21,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 25,31</t>
+          <t>16,31; 26,06</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,93; 26,06</t>
+          <t>17,13; 26,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,79; 24,58</t>
+          <t>15,75; 25,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 24,97</t>
+          <t>16,0; 25,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 31,52</t>
+          <t>17,8; 31,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,5; 23,74</t>
+          <t>15,09; 24,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,14; 22,73</t>
+          <t>14,24; 22,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,44; 22,5</t>
+          <t>14,45; 22,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,35; 30,24</t>
+          <t>20,73; 30,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,44; 23,48</t>
+          <t>17,5; 23,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,73; 22,12</t>
+          <t>16,1; 22,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,51; 22,7</t>
+          <t>16,52; 22,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,9; 29,09</t>
+          <t>20,9; 29,06</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,41; 23,77</t>
+          <t>13,56; 24,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,7; 27,01</t>
+          <t>16,64; 26,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 22,96</t>
+          <t>13,39; 22,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,11; 64,34</t>
+          <t>29,01; 61,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,47; 29,67</t>
+          <t>18,03; 29,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,49; 27,66</t>
+          <t>17,42; 27,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 21,78</t>
+          <t>12,5; 22,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,21; 37,67</t>
+          <t>24,8; 39,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,27; 24,89</t>
+          <t>17,32; 25,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 25,5</t>
+          <t>18,52; 25,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,25; 21,06</t>
+          <t>14,25; 20,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,14; 53,69</t>
+          <t>29,4; 50,54</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 16,37</t>
+          <t>8,77; 16,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,44; 24,88</t>
+          <t>15,0; 24,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,04; 21,08</t>
+          <t>11,56; 20,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,88; 23,5</t>
+          <t>13,82; 23,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,81; 23,36</t>
+          <t>14,57; 23,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,37; 27,57</t>
+          <t>17,73; 28,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 19,06</t>
+          <t>11,23; 19,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,44; 23,73</t>
+          <t>13,92; 24,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,67; 18,4</t>
+          <t>12,7; 18,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,02; 25,1</t>
+          <t>17,79; 24,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,21; 18,18</t>
+          <t>12,49; 18,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,18; 21,92</t>
+          <t>15,18; 22,2</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,07; 20,79</t>
+          <t>16,3; 20,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,23</t>
+          <t>18,31; 23,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,72; 20,56</t>
+          <t>15,78; 20,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,39; 37,97</t>
+          <t>22,44; 38,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,63; 22,56</t>
+          <t>17,64; 22,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,59; 23,46</t>
+          <t>18,66; 23,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,34; 18,82</t>
+          <t>14,4; 19,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,87; 26,87</t>
+          <t>21,35; 27,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,66; 20,86</t>
+          <t>17,47; 20,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,17; 22,72</t>
+          <t>19,25; 22,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,61; 18,91</t>
+          <t>15,79; 18,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,74; 31,08</t>
+          <t>22,75; 30,58</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>32818</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31446</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24359</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25841</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>27660</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>61492</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>65870</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>48536</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>53501</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>25622; 41553</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23771; 40933</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17420; 32912</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19120; 34011</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>21434; 37497</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>26504; 44267</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16952; 32556</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>19082; 38085</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>51261; 73043</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>54911; 79280</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>37764; 60431</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>42028; 67142</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>41647</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>41504</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>42699</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44242</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>63809</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>82952</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>81824</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>83846</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>108051</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>33432; 51093</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>32507; 51747</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>33166; 51849</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>33907; 60127</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>32015; 51120</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>31881; 50781</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>32413; 51232</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>52720; 77082</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>71268; 95140</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>69276; 96157</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>71293; 97469</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>92989; 129280</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>25164</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32964</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27615</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>77071</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36601</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>56923</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>60286</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>69565</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>55421</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>133994</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>18687; 33139</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25851; 41887</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20882; 35830</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53986; 115287</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>26981; 43557</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>29015; 45461</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20841; 37077</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>45957; 73137</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>49796; 72359</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>59635; 82745</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>45984; 67609</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>109171; 187674</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>25677</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41786</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32788</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30561</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>33809</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>64494</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>89015</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>62934</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>64371</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>18353; 33837</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31551; 51879</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>23978; 42423</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>23220; 38833</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>30275; 48549</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>36687; 58272</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>23096; 39622</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>25221; 43758</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>52990; 76821</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>74205; 102339</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>51603; 76081</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>53000; 77531</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>125305</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>147701</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>127461</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>177715</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>182201</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>269224</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>306275</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>250737</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>359916</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>110980; 142532</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>130280; 167322</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>111129; 144884</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148523; 256457</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>127498; 161419</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>140344; 177591</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>107274; 142274</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>162543; 206332</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>245290; 292494</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>281654; 332147</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>228851; 273319</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>323800; 435188</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP15-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,47; 29,95</t>
+          <t>18,4; 30,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,06; 29,37</t>
+          <t>17,31; 29,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,03; 24,61</t>
+          <t>13,14; 24,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,3; 29,0</t>
+          <t>17,06; 29,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,0; 24,5</t>
+          <t>14,22; 24,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 28,62</t>
+          <t>17,3; 28,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,45; 21,99</t>
+          <t>11,67; 22,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,59; 27,12</t>
+          <t>13,62; 26,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,57; 25,03</t>
+          <t>17,22; 25,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,67; 26,96</t>
+          <t>18,71; 27,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,4; 21,45</t>
+          <t>13,7; 21,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,31; 26,06</t>
+          <t>16,26; 25,83</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,13; 26,18</t>
+          <t>16,7; 26,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,75; 25,08</t>
+          <t>16,2; 25,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,0; 25,02</t>
+          <t>16,5; 24,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,8; 31,56</t>
+          <t>17,59; 31,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,09; 24,1</t>
+          <t>15,51; 24,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,24; 22,69</t>
+          <t>14,13; 22,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,45; 22,83</t>
+          <t>14,4; 23,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,73; 30,31</t>
+          <t>20,33; 30,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,5; 23,36</t>
+          <t>17,23; 23,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,1; 22,35</t>
+          <t>16,14; 22,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,52; 22,58</t>
+          <t>16,78; 22,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,9; 29,06</t>
+          <t>20,74; 28,83</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,56; 24,05</t>
+          <t>13,97; 23,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,64; 26,96</t>
+          <t>16,76; 26,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,39; 22,97</t>
+          <t>13,18; 22,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,01; 61,95</t>
+          <t>29,74; 63,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,03; 29,1</t>
+          <t>18,13; 29,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 27,29</t>
+          <t>17,18; 27,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,5; 22,25</t>
+          <t>12,3; 22,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,8; 39,47</t>
+          <t>24,06; 38,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,32; 25,17</t>
+          <t>17,3; 24,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,52; 25,7</t>
+          <t>18,12; 25,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,25; 20,95</t>
+          <t>13,93; 20,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,4; 50,54</t>
+          <t>29,62; 49,82</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 16,17</t>
+          <t>8,68; 16,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,0; 24,67</t>
+          <t>15,84; 25,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 20,45</t>
+          <t>11,71; 20,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,82; 23,12</t>
+          <t>13,86; 23,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,57; 23,36</t>
+          <t>14,69; 23,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,73; 28,16</t>
+          <t>18,03; 28,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,23; 19,26</t>
+          <t>10,76; 19,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,92; 24,14</t>
+          <t>14,23; 24,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,7; 18,42</t>
+          <t>12,8; 18,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,79; 24,53</t>
+          <t>17,84; 24,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,49; 18,41</t>
+          <t>12,48; 18,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,18; 22,2</t>
+          <t>15,19; 22,05</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,3; 20,93</t>
+          <t>16,22; 20,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,31; 23,52</t>
+          <t>18,36; 23,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,78; 20,57</t>
+          <t>15,79; 20,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,44; 38,75</t>
+          <t>22,28; 37,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,64; 22,34</t>
+          <t>17,66; 22,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,66; 23,62</t>
+          <t>18,72; 23,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,4; 19,1</t>
+          <t>14,51; 19,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,35; 27,1</t>
+          <t>21,02; 27,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 20,84</t>
+          <t>17,57; 20,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,25; 22,7</t>
+          <t>19,11; 22,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,79; 18,86</t>
+          <t>15,71; 18,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,75; 30,58</t>
+          <t>22,79; 29,94</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25622; 41553</t>
+          <t>25519; 42347</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23771; 40933</t>
+          <t>24125; 41410</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17420; 32912</t>
+          <t>17566; 33238</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19120; 34011</t>
+          <t>20002; 34665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21434; 37497</t>
+          <t>21775; 37424</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26504; 44267</t>
+          <t>26762; 43873</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16952; 32556</t>
+          <t>17286; 33144</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19082; 38085</t>
+          <t>19121; 37800</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51261; 73043</t>
+          <t>50263; 73229</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54911; 79280</t>
+          <t>55021; 79399</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37764; 60431</t>
+          <t>38616; 60158</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42028; 67142</t>
+          <t>41905; 66570</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33432; 51093</t>
+          <t>32587; 51275</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32507; 51747</t>
+          <t>33423; 51685</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33166; 51849</t>
+          <t>34202; 51559</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33907; 60127</t>
+          <t>33513; 60861</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32015; 51120</t>
+          <t>32906; 51416</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31881; 50781</t>
+          <t>31626; 50175</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32413; 51232</t>
+          <t>32317; 51674</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52720; 77082</t>
+          <t>51700; 76998</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71268; 95140</t>
+          <t>70169; 96145</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69276; 96157</t>
+          <t>69413; 95513</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71293; 97469</t>
+          <t>72421; 97467</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92989; 129280</t>
+          <t>92273; 128242</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18687; 33139</t>
+          <t>19252; 32992</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25851; 41887</t>
+          <t>26041; 41684</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20882; 35830</t>
+          <t>20565; 35256</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53986; 115287</t>
+          <t>55342; 118431</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26981; 43557</t>
+          <t>27136; 44083</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29015; 45461</t>
+          <t>28620; 46011</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20841; 37077</t>
+          <t>20493; 37071</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45957; 73137</t>
+          <t>44587; 70521</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>49796; 72359</t>
+          <t>49730; 71064</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59635; 82745</t>
+          <t>58348; 83209</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45984; 67609</t>
+          <t>44947; 66925</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>109171; 187674</t>
+          <t>110008; 185016</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18353; 33837</t>
+          <t>18171; 34822</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31551; 51879</t>
+          <t>33302; 52943</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23978; 42423</t>
+          <t>24286; 42373</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23220; 38833</t>
+          <t>23275; 39169</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30275; 48549</t>
+          <t>30538; 49432</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36687; 58272</t>
+          <t>37303; 58458</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23096; 39622</t>
+          <t>22128; 39271</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25221; 43758</t>
+          <t>25785; 44740</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52990; 76821</t>
+          <t>53397; 77299</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74205; 102339</t>
+          <t>74446; 102910</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51603; 76081</t>
+          <t>51577; 76673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53000; 77531</t>
+          <t>53060; 77008</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>110980; 142532</t>
+          <t>110452; 142934</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>130280; 167322</t>
+          <t>130633; 166963</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111129; 144884</t>
+          <t>111243; 143709</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148523; 256457</t>
+          <t>147455; 245221</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>127498; 161419</t>
+          <t>127646; 162371</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>140344; 177591</t>
+          <t>140740; 177977</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>107274; 142274</t>
+          <t>108085; 141931</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>162543; 206332</t>
+          <t>160032; 206571</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>245290; 292494</t>
+          <t>246620; 293691</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>281654; 332147</t>
+          <t>279624; 331255</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>228851; 273319</t>
+          <t>227717; 273513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>323800; 435188</t>
+          <t>324265; 426090</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP15-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP15-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18,73%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22,25%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>23,66%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>22,57%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>18,22%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22,03%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,4; 30,53</t>
+          <t>14,05; 24,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,31; 29,72</t>
+          <t>16,51; 27,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,14; 24,86</t>
+          <t>11,61; 22,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,06; 29,56</t>
+          <t>13,19; 26,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,22; 24,45</t>
+          <t>18,17; 30,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,3; 28,36</t>
+          <t>16,14; 28,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,67; 22,38</t>
+          <t>13,42; 24,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,62; 26,92</t>
+          <t>16,14; 28,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 25,1</t>
+          <t>17,77; 25,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,71; 27,0</t>
+          <t>18,64; 27,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,7; 21,35</t>
+          <t>13,42; 21,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,26; 25,83</t>
+          <t>16,29; 25,07</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18,01%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18,34%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>21,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>20,11%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>20,6%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23,22%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,7; 26,27</t>
+          <t>15,5; 23,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,2; 25,05</t>
+          <t>14,14; 22,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,5; 24,88</t>
+          <t>14,44; 22,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,59; 31,95</t>
+          <t>19,27; 29,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,51; 24,24</t>
+          <t>16,93; 26,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,13; 22,42</t>
+          <t>15,79; 24,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,4; 23,03</t>
+          <t>16,3; 24,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,33; 30,28</t>
+          <t>15,02; 24,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,23; 23,61</t>
+          <t>17,44; 23,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,14; 22,2</t>
+          <t>15,73; 22,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,78; 22,58</t>
+          <t>16,51; 22,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,74; 28,83</t>
+          <t>18,92; 26,18</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23,47%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21,97%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,68%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>31,1%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>18,26%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>21,22%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>17,7%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>41,42%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,68%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,97; 23,94</t>
+          <t>18,47; 29,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,76; 26,83</t>
+          <t>17,49; 27,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,18; 22,6</t>
+          <t>12,45; 21,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,74; 63,64</t>
+          <t>24,45; 38,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,13; 29,46</t>
+          <t>13,41; 23,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,18; 27,62</t>
+          <t>16,7; 27,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,3; 22,24</t>
+          <t>13,52; 22,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,06; 38,06</t>
+          <t>26,3; 39,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,3; 24,72</t>
+          <t>17,27; 24,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,12; 25,84</t>
+          <t>18,28; 25,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,93; 20,74</t>
+          <t>14,25; 21,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,62; 49,82</t>
+          <t>27,09; 37,19</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18,68%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18,61%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>12,27%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>19,87%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>17,78%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>15,46%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>21,34%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18,2%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,68%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18,65%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>21,34%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,68; 16,64</t>
+          <t>14,81; 23,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,84; 25,17</t>
+          <t>18,37; 27,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,71; 20,43</t>
+          <t>10,56; 19,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,86; 23,32</t>
+          <t>14,43; 23,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,69; 23,79</t>
+          <t>8,58; 16,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,03; 28,25</t>
+          <t>15,44; 24,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 19,09</t>
+          <t>12,04; 21,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,23; 24,69</t>
+          <t>13,68; 22,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,8; 18,53</t>
+          <t>12,67; 18,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,84; 24,67</t>
+          <t>18,02; 25,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 18,56</t>
+          <t>12,21; 18,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,19; 22,05</t>
+          <t>14,87; 21,53</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21,09%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>18,4%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20,76%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>18,1%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,22; 20,99</t>
+          <t>17,63; 22,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,36; 23,47</t>
+          <t>18,59; 23,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,79; 20,4</t>
+          <t>14,34; 18,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,28; 37,05</t>
+          <t>20,52; 26,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,66; 22,47</t>
+          <t>16,07; 20,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,72; 23,67</t>
+          <t>18,26; 23,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,51; 19,06</t>
+          <t>15,72; 20,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,02; 27,14</t>
+          <t>19,99; 25,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,57; 20,92</t>
+          <t>17,66; 20,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,11; 22,64</t>
+          <t>19,17; 22,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,71; 18,87</t>
+          <t>15,61; 18,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,79; 29,94</t>
+          <t>21,28; 25,44</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..) (tasa de respuesta: 99,95%)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25519; 42347</t>
+          <t>21507; 37185</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24125; 41410</t>
+          <t>25539; 43095</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17566; 33238</t>
+          <t>17192; 33090</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20002; 34665</t>
+          <t>16613; 32822</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21775; 37424</t>
+          <t>25211; 41703</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26762; 43873</t>
+          <t>22498; 40196</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17286; 33144</t>
+          <t>17950; 33351</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19121; 37800</t>
+          <t>19545; 34232</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50263; 73229</t>
+          <t>51849; 74540</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55021; 79399</t>
+          <t>54816; 79382</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38616; 60158</t>
+          <t>37816; 59723</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41905; 66570</t>
+          <t>40236; 61929</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>41504</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92593</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32587; 51275</t>
+          <t>32883; 50353</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33423; 51685</t>
+          <t>31653; 50872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34202; 51559</t>
+          <t>32397; 50473</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33513; 60861</t>
+          <t>45598; 68627</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32906; 51416</t>
+          <t>33035; 50854</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31626; 50175</t>
+          <t>32578; 50714</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32317; 51674</t>
+          <t>33790; 51745</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51700; 76998</t>
+          <t>27696; 45710</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70169; 96145</t>
+          <t>71017; 95645</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69413; 95513</t>
+          <t>67686; 95142</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72421; 97467</t>
+          <t>71238; 97973</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92273; 128242</t>
+          <t>79668; 110232</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>73</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36601</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36601</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19252; 32992</t>
+          <t>27649; 44398</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26041; 41684</t>
+          <t>29131; 46076</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20565; 35256</t>
+          <t>20752; 36298</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55342; 118431</t>
+          <t>41161; 64326</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27136; 44083</t>
+          <t>18477; 32762</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28620; 46011</t>
+          <t>25942; 41961</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20493; 37071</t>
+          <t>21094; 35818</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>44587; 70521</t>
+          <t>40857; 61435</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>49730; 71064</t>
+          <t>49657; 71559</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58348; 83209</t>
+          <t>58862; 82115</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44947; 66925</t>
+          <t>45986; 67968</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>110008; 185016</t>
+          <t>87695; 120386</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>47</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64371</t>
+          <t>61240</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18171; 34822</t>
+          <t>30782; 48554</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33302; 52943</t>
+          <t>37998; 57031</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24286; 42373</t>
+          <t>21729; 39215</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23275; 39169</t>
+          <t>24443; 40196</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30538; 49432</t>
+          <t>17958; 34263</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37303; 58458</t>
+          <t>32481; 52330</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22128; 39271</t>
+          <t>24983; 43717</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25785; 44740</t>
+          <t>22864; 38314</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53397; 77299</t>
+          <t>52843; 76772</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74446; 102910</t>
+          <t>75194; 104709</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51577; 76673</t>
+          <t>50451; 75114</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53060; 77008</t>
+          <t>50035; 72443</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>226</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>110452; 142934</t>
+          <t>127434; 163024</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>130633; 166963</t>
+          <t>139830; 176392</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111243; 143709</t>
+          <t>106791; 140198</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>147455; 245221</t>
+          <t>143688; 185319</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>127646; 162371</t>
+          <t>109450; 141613</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>140740; 177977</t>
+          <t>129929; 165279</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>108085; 141931</t>
+          <t>110759; 144834</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>160032; 206571</t>
+          <t>125557; 161697</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>246620; 293691</t>
+          <t>247844; 292802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>279624; 331255</t>
+          <t>280503; 332508</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>227717; 273513</t>
+          <t>226261; 274110</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>324265; 426090</t>
+          <t>282577; 337946</t>
         </is>
       </c>
     </row>
